--- a/uploads/Les 12 principes version final 22-02-2024.xlsx
+++ b/uploads/Les 12 principes version final 22-02-2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moham\Desktop\pfe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A364772-5D5A-4C42-B1A1-360DEA28A85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D936ABD-0F31-4FBE-8696-7B0C0EB2D3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="956" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="956" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Finalité" sheetId="13" r:id="rId1"/>
@@ -3143,38 +3143,26 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3233,9 +3221,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3251,11 +3236,17 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3271,18 +3262,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3365,35 +3344,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3409,24 +3427,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3724,17 +3724,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="67"/>
@@ -3748,32 +3748,32 @@
       <c r="I2" s="67"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="142" t="s">
+      <c r="A3" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="142" t="s">
+      <c r="B3" s="138" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="142" t="s">
+      <c r="C3" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="142" t="s">
+      <c r="D3" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="142"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="142"/>
-      <c r="H3" s="142" t="s">
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="138" t="s">
         <v>260</v>
       </c>
-      <c r="I3" s="142" t="s">
+      <c r="I3" s="138" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="142"/>
-      <c r="B4" s="142"/>
-      <c r="C4" s="142"/>
+      <c r="A4" s="138"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="138"/>
       <c r="D4" s="46">
         <v>0</v>
       </c>
@@ -3786,13 +3786,13 @@
       <c r="G4" s="46">
         <v>3</v>
       </c>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="142"/>
-      <c r="B5" s="143"/>
-      <c r="C5" s="143"/>
+      <c r="A5" s="138"/>
+      <c r="B5" s="139"/>
+      <c r="C5" s="139"/>
       <c r="D5" s="47" t="s">
         <v>4</v>
       </c>
@@ -3805,14 +3805,14 @@
       <c r="G5" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="142"/>
-      <c r="I5" s="142"/>
+      <c r="H5" s="138"/>
+      <c r="I5" s="138"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="32">
         <v>1</v>
       </c>
-      <c r="B6" s="138" t="s">
+      <c r="B6" s="134" t="s">
         <v>222</v>
       </c>
       <c r="C6" s="49" t="s">
@@ -3829,7 +3829,7 @@
       <c r="A7" s="32">
         <v>2</v>
       </c>
-      <c r="B7" s="139"/>
+      <c r="B7" s="135"/>
       <c r="C7" s="65" t="s">
         <v>225</v>
       </c>
@@ -3848,7 +3848,7 @@
       <c r="A8" s="32">
         <v>3</v>
       </c>
-      <c r="B8" s="139"/>
+      <c r="B8" s="135"/>
       <c r="C8" s="65" t="s">
         <v>226</v>
       </c>
@@ -3867,7 +3867,7 @@
       <c r="A9" s="32">
         <v>4</v>
       </c>
-      <c r="B9" s="139"/>
+      <c r="B9" s="135"/>
       <c r="C9" s="65" t="s">
         <v>228</v>
       </c>
@@ -3886,7 +3886,7 @@
       <c r="A10" s="32">
         <v>5</v>
       </c>
-      <c r="B10" s="139"/>
+      <c r="B10" s="135"/>
       <c r="C10" s="65" t="s">
         <v>230</v>
       </c>
@@ -3905,7 +3905,7 @@
       <c r="A11" s="32">
         <v>6</v>
       </c>
-      <c r="B11" s="139"/>
+      <c r="B11" s="135"/>
       <c r="C11" s="66" t="s">
         <v>219</v>
       </c>
@@ -3922,7 +3922,7 @@
       <c r="A12" s="32">
         <v>7</v>
       </c>
-      <c r="B12" s="139"/>
+      <c r="B12" s="135"/>
       <c r="C12" s="65" t="s">
         <v>218</v>
       </c>
@@ -3941,7 +3941,7 @@
       <c r="A13" s="32">
         <v>9</v>
       </c>
-      <c r="B13" s="139"/>
+      <c r="B13" s="135"/>
       <c r="C13" s="50" t="s">
         <v>220</v>
       </c>
@@ -3960,7 +3960,7 @@
       <c r="A14" s="32">
         <v>10</v>
       </c>
-      <c r="B14" s="139"/>
+      <c r="B14" s="135"/>
       <c r="C14" s="65" t="s">
         <v>221</v>
       </c>
@@ -3979,7 +3979,7 @@
       <c r="A15" s="32">
         <v>11</v>
       </c>
-      <c r="B15" s="138" t="s">
+      <c r="B15" s="134" t="s">
         <v>235</v>
       </c>
       <c r="C15" s="65" t="s">
@@ -4000,7 +4000,7 @@
       <c r="A16" s="32">
         <v>12</v>
       </c>
-      <c r="B16" s="140"/>
+      <c r="B16" s="136"/>
       <c r="C16" s="66" t="s">
         <v>236</v>
       </c>
@@ -4051,47 +4051,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="130" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="163" t="s">
+      <c r="A4" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="163" t="s">
+      <c r="B4" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="163" t="s">
+      <c r="C4" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="163" t="s">
+      <c r="D4" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="163"/>
-      <c r="F4" s="163"/>
-      <c r="G4" s="163"/>
-      <c r="H4" s="163" t="s">
+      <c r="E4" s="131"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="163" t="s">
+      <c r="I4" s="131" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="163"/>
-      <c r="B5" s="163"/>
-      <c r="C5" s="163"/>
+      <c r="A5" s="131"/>
+      <c r="B5" s="131"/>
+      <c r="C5" s="131"/>
       <c r="D5" s="19">
         <v>0</v>
       </c>
@@ -4104,13 +4104,13 @@
       <c r="G5" s="19">
         <v>3</v>
       </c>
-      <c r="H5" s="163"/>
-      <c r="I5" s="163"/>
+      <c r="H5" s="131"/>
+      <c r="I5" s="131"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="163"/>
-      <c r="B6" s="164"/>
-      <c r="C6" s="164"/>
+      <c r="A6" s="131"/>
+      <c r="B6" s="132"/>
+      <c r="C6" s="132"/>
       <c r="D6" s="29" t="s">
         <v>4</v>
       </c>
@@ -4123,8 +4123,8 @@
       <c r="G6" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="163"/>
-      <c r="I6" s="163"/>
+      <c r="H6" s="131"/>
+      <c r="I6" s="131"/>
     </row>
     <row r="7" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="19">
@@ -4251,7 +4251,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="206" t="s">
+      <c r="H13" s="209" t="s">
         <v>20</v>
       </c>
       <c r="I13" s="1"/>
@@ -4269,7 +4269,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="184"/>
+      <c r="H14" s="177"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -4353,47 +4353,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
       <c r="J1" s="16"/>
       <c r="K1" s="16"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="163" t="s">
+      <c r="A3" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="163" t="s">
+      <c r="B3" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="207" t="s">
+      <c r="C3" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="163" t="s">
+      <c r="D3" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163" t="s">
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
+      <c r="H3" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="163" t="s">
+      <c r="I3" s="131" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="163"/>
-      <c r="B4" s="163"/>
-      <c r="C4" s="208"/>
+      <c r="A4" s="131"/>
+      <c r="B4" s="131"/>
+      <c r="C4" s="128"/>
       <c r="D4" s="19">
         <v>0</v>
       </c>
@@ -4406,13 +4406,13 @@
       <c r="G4" s="19">
         <v>3</v>
       </c>
-      <c r="H4" s="163"/>
-      <c r="I4" s="163"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="131"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="163"/>
-      <c r="B5" s="164"/>
-      <c r="C5" s="157"/>
+      <c r="A5" s="131"/>
+      <c r="B5" s="132"/>
+      <c r="C5" s="133"/>
       <c r="D5" s="29" t="s">
         <v>4</v>
       </c>
@@ -4425,14 +4425,14 @@
       <c r="G5" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="163"/>
-      <c r="I5" s="163"/>
+      <c r="H5" s="131"/>
+      <c r="I5" s="131"/>
     </row>
     <row r="6" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="19">
         <v>1</v>
       </c>
-      <c r="B6" s="207" t="s">
+      <c r="B6" s="127" t="s">
         <v>96</v>
       </c>
       <c r="C6" s="21" t="s">
@@ -4451,7 +4451,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="19"/>
-      <c r="B7" s="208"/>
+      <c r="B7" s="128"/>
       <c r="C7" s="22" t="s">
         <v>128</v>
       </c>
@@ -4466,7 +4466,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="19"/>
-      <c r="B8" s="208"/>
+      <c r="B8" s="128"/>
       <c r="C8" s="22" t="s">
         <v>98</v>
       </c>
@@ -4481,7 +4481,7 @@
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19"/>
-      <c r="B9" s="209"/>
+      <c r="B9" s="129"/>
       <c r="C9" s="23" t="s">
         <v>79</v>
       </c>
@@ -4498,7 +4498,7 @@
       <c r="A10" s="19">
         <v>2</v>
       </c>
-      <c r="B10" s="207" t="s">
+      <c r="B10" s="127" t="s">
         <v>79</v>
       </c>
       <c r="C10" s="22" t="s">
@@ -4515,7 +4515,7 @@
     </row>
     <row r="11" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="19"/>
-      <c r="B11" s="208"/>
+      <c r="B11" s="128"/>
       <c r="C11" s="23" t="s">
         <v>102</v>
       </c>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="19"/>
-      <c r="B12" s="209"/>
+      <c r="B12" s="129"/>
       <c r="C12" s="22" t="s">
         <v>101</v>
       </c>
@@ -4547,7 +4547,7 @@
       <c r="A13" s="19">
         <v>3</v>
       </c>
-      <c r="B13" s="207" t="s">
+      <c r="B13" s="127" t="s">
         <v>99</v>
       </c>
       <c r="D13" s="3"/>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="19"/>
-      <c r="B14" s="208"/>
+      <c r="B14" s="128"/>
       <c r="C14" s="23" t="s">
         <v>103</v>
       </c>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="19"/>
-      <c r="B15" s="209"/>
+      <c r="B15" s="129"/>
       <c r="C15" s="23" t="s">
         <v>104</v>
       </c>
@@ -4682,45 +4682,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="163" t="s">
+      <c r="A3" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="163" t="s">
+      <c r="B3" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="163" t="s">
+      <c r="C3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="163" t="s">
+      <c r="D3" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163" t="s">
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
+      <c r="H3" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="163" t="s">
+      <c r="I3" s="131" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="163"/>
-      <c r="B4" s="163"/>
-      <c r="C4" s="163"/>
+      <c r="A4" s="131"/>
+      <c r="B4" s="131"/>
+      <c r="C4" s="131"/>
       <c r="D4" s="19">
         <v>0</v>
       </c>
@@ -4733,13 +4733,13 @@
       <c r="G4" s="19">
         <v>3</v>
       </c>
-      <c r="H4" s="163"/>
-      <c r="I4" s="163"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="131"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="163"/>
-      <c r="B5" s="164"/>
-      <c r="C5" s="164"/>
+      <c r="A5" s="131"/>
+      <c r="B5" s="132"/>
+      <c r="C5" s="132"/>
       <c r="D5" s="19" t="s">
         <v>4</v>
       </c>
@@ -4752,14 +4752,14 @@
       <c r="G5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="163"/>
-      <c r="I5" s="163"/>
+      <c r="H5" s="131"/>
+      <c r="I5" s="131"/>
     </row>
     <row r="6" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="20">
         <v>1</v>
       </c>
-      <c r="B6" s="210" t="s">
+      <c r="B6" s="216" t="s">
         <v>45</v>
       </c>
       <c r="C6" s="62" t="s">
@@ -4772,7 +4772,7 @@
       <c r="H6" s="52" t="s">
         <v>182</v>
       </c>
-      <c r="I6" s="215" t="s">
+      <c r="I6" s="210" t="s">
         <v>183</v>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
       <c r="A7" s="20">
         <v>2</v>
       </c>
-      <c r="B7" s="211"/>
+      <c r="B7" s="217"/>
       <c r="C7" s="62" t="s">
         <v>55</v>
       </c>
@@ -4791,13 +4791,13 @@
       <c r="H7" s="61" t="s">
         <v>197</v>
       </c>
-      <c r="I7" s="216"/>
+      <c r="I7" s="211"/>
     </row>
     <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="20">
         <v>3</v>
       </c>
-      <c r="B8" s="211"/>
+      <c r="B8" s="217"/>
       <c r="C8" s="62" t="s">
         <v>198</v>
       </c>
@@ -4808,13 +4808,13 @@
       <c r="H8" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="I8" s="216"/>
+      <c r="I8" s="211"/>
     </row>
     <row r="9" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="20">
         <v>4</v>
       </c>
-      <c r="B9" s="211"/>
+      <c r="B9" s="217"/>
       <c r="C9" s="62" t="s">
         <v>199</v>
       </c>
@@ -4825,13 +4825,13 @@
       <c r="H9" s="61" t="s">
         <v>200</v>
       </c>
-      <c r="I9" s="216"/>
+      <c r="I9" s="211"/>
     </row>
     <row r="10" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="20">
         <v>5</v>
       </c>
-      <c r="B10" s="212"/>
+      <c r="B10" s="218"/>
       <c r="C10" s="62" t="s">
         <v>56</v>
       </c>
@@ -4842,13 +4842,13 @@
       <c r="H10" s="61" t="s">
         <v>201</v>
       </c>
-      <c r="I10" s="217"/>
+      <c r="I10" s="212"/>
     </row>
     <row r="11" spans="1:9" ht="105.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="20">
         <v>6</v>
       </c>
-      <c r="B11" s="213" t="s">
+      <c r="B11" s="219" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="62" t="s">
@@ -4861,7 +4861,7 @@
       <c r="H11" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="I11" s="215" t="s">
+      <c r="I11" s="210" t="s">
         <v>185</v>
       </c>
     </row>
@@ -4869,7 +4869,7 @@
       <c r="A12" s="20">
         <v>7</v>
       </c>
-      <c r="B12" s="139"/>
+      <c r="B12" s="135"/>
       <c r="C12" s="62" t="s">
         <v>58</v>
       </c>
@@ -4880,13 +4880,13 @@
       <c r="H12" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="I12" s="216"/>
+      <c r="I12" s="211"/>
     </row>
     <row r="13" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="20">
         <v>8</v>
       </c>
-      <c r="B13" s="139"/>
+      <c r="B13" s="135"/>
       <c r="C13" s="62" t="s">
         <v>59</v>
       </c>
@@ -4897,13 +4897,13 @@
       <c r="H13" s="63" t="s">
         <v>204</v>
       </c>
-      <c r="I13" s="216"/>
+      <c r="I13" s="211"/>
     </row>
     <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="20">
         <v>9</v>
       </c>
-      <c r="B14" s="139"/>
+      <c r="B14" s="135"/>
       <c r="C14" s="64" t="s">
         <v>205</v>
       </c>
@@ -4914,13 +4914,13 @@
       <c r="H14" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="I14" s="216"/>
+      <c r="I14" s="211"/>
     </row>
     <row r="15" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="20">
         <v>10</v>
       </c>
-      <c r="B15" s="139"/>
+      <c r="B15" s="135"/>
       <c r="C15" s="62" t="s">
         <v>60</v>
       </c>
@@ -4931,13 +4931,13 @@
       <c r="H15" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="I15" s="216"/>
+      <c r="I15" s="211"/>
     </row>
     <row r="16" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="20">
         <v>11</v>
       </c>
-      <c r="B16" s="139"/>
+      <c r="B16" s="135"/>
       <c r="C16" s="62" t="s">
         <v>61</v>
       </c>
@@ -4948,13 +4948,13 @@
       <c r="H16" s="61" t="s">
         <v>206</v>
       </c>
-      <c r="I16" s="216"/>
+      <c r="I16" s="211"/>
     </row>
     <row r="17" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="20">
         <v>12</v>
       </c>
-      <c r="B17" s="139"/>
+      <c r="B17" s="135"/>
       <c r="C17" s="62" t="s">
         <v>62</v>
       </c>
@@ -4965,13 +4965,13 @@
       <c r="H17" s="61" t="s">
         <v>207</v>
       </c>
-      <c r="I17" s="216"/>
+      <c r="I17" s="211"/>
     </row>
     <row r="18" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="20">
         <v>13</v>
       </c>
-      <c r="B18" s="214"/>
+      <c r="B18" s="220"/>
       <c r="C18" s="64" t="s">
         <v>208</v>
       </c>
@@ -4982,13 +4982,13 @@
       <c r="H18" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="I18" s="217"/>
+      <c r="I18" s="212"/>
     </row>
     <row r="19" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A19" s="20">
         <v>14</v>
       </c>
-      <c r="B19" s="213" t="s">
+      <c r="B19" s="219" t="s">
         <v>48</v>
       </c>
       <c r="C19" s="62" t="s">
@@ -5001,7 +5001,7 @@
       <c r="H19" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="I19" s="218" t="s">
+      <c r="I19" s="213" t="s">
         <v>188</v>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       <c r="A20" s="20">
         <v>15</v>
       </c>
-      <c r="B20" s="139"/>
+      <c r="B20" s="135"/>
       <c r="C20" s="62" t="s">
         <v>65</v>
       </c>
@@ -5020,13 +5020,13 @@
       <c r="H20" s="61" t="s">
         <v>210</v>
       </c>
-      <c r="I20" s="166"/>
+      <c r="I20" s="163"/>
     </row>
     <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="20">
         <v>16</v>
       </c>
-      <c r="B21" s="139"/>
+      <c r="B21" s="135"/>
       <c r="C21" s="62" t="s">
         <v>66</v>
       </c>
@@ -5037,13 +5037,13 @@
       <c r="H21" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="I21" s="166"/>
+      <c r="I21" s="163"/>
     </row>
     <row r="22" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A22" s="20">
         <v>17</v>
       </c>
-      <c r="B22" s="139"/>
+      <c r="B22" s="135"/>
       <c r="C22" s="62" t="s">
         <v>67</v>
       </c>
@@ -5054,13 +5054,13 @@
       <c r="H22" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="I22" s="166"/>
+      <c r="I22" s="163"/>
     </row>
     <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="20">
         <v>18</v>
       </c>
-      <c r="B23" s="214"/>
+      <c r="B23" s="220"/>
       <c r="C23" s="62" t="s">
         <v>68</v>
       </c>
@@ -5071,13 +5071,13 @@
       <c r="H23" s="61" t="s">
         <v>212</v>
       </c>
-      <c r="I23" s="167"/>
+      <c r="I23" s="164"/>
     </row>
     <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="20">
         <v>19</v>
       </c>
-      <c r="B24" s="213" t="s">
+      <c r="B24" s="219" t="s">
         <v>47</v>
       </c>
       <c r="C24" s="62" t="s">
@@ -5090,7 +5090,7 @@
       <c r="H24" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="I24" s="219" t="s">
+      <c r="I24" s="214" t="s">
         <v>191</v>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       <c r="A25" s="20">
         <v>20</v>
       </c>
-      <c r="B25" s="139"/>
+      <c r="B25" s="135"/>
       <c r="C25" s="64" t="s">
         <v>213</v>
       </c>
@@ -5109,13 +5109,13 @@
       <c r="H25" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="I25" s="179"/>
+      <c r="I25" s="172"/>
     </row>
     <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="20">
         <v>21</v>
       </c>
-      <c r="B26" s="139"/>
+      <c r="B26" s="135"/>
       <c r="C26" s="62" t="s">
         <v>70</v>
       </c>
@@ -5126,13 +5126,13 @@
       <c r="H26" s="61" t="s">
         <v>215</v>
       </c>
-      <c r="I26" s="179"/>
+      <c r="I26" s="172"/>
     </row>
     <row r="27" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A27" s="20">
         <v>22</v>
       </c>
-      <c r="B27" s="214"/>
+      <c r="B27" s="220"/>
       <c r="C27" s="62" t="s">
         <v>71</v>
       </c>
@@ -5143,13 +5143,13 @@
       <c r="H27" s="61" t="s">
         <v>216</v>
       </c>
-      <c r="I27" s="180"/>
+      <c r="I27" s="173"/>
     </row>
     <row r="28" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A28" s="20">
         <v>23</v>
       </c>
-      <c r="B28" s="213" t="s">
+      <c r="B28" s="219" t="s">
         <v>49</v>
       </c>
       <c r="C28" s="62" t="s">
@@ -5162,7 +5162,7 @@
       <c r="H28" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="I28" s="220" t="s">
+      <c r="I28" s="215" t="s">
         <v>193</v>
       </c>
     </row>
@@ -5170,7 +5170,7 @@
       <c r="A29" s="20">
         <v>24</v>
       </c>
-      <c r="B29" s="139"/>
+      <c r="B29" s="135"/>
       <c r="C29" s="62" t="s">
         <v>73</v>
       </c>
@@ -5181,13 +5181,13 @@
       <c r="H29" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="I29" s="176"/>
+      <c r="I29" s="169"/>
     </row>
     <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="20">
         <v>25</v>
       </c>
-      <c r="B30" s="139"/>
+      <c r="B30" s="135"/>
       <c r="C30" s="62" t="s">
         <v>74</v>
       </c>
@@ -5198,13 +5198,13 @@
       <c r="H30" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="I30" s="176"/>
+      <c r="I30" s="169"/>
     </row>
     <row r="31" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="20">
         <v>26</v>
       </c>
-      <c r="B31" s="214"/>
+      <c r="B31" s="220"/>
       <c r="C31" s="62" t="s">
         <v>75</v>
       </c>
@@ -5215,10 +5215,20 @@
       <c r="H31" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="I31" s="177"/>
+      <c r="I31" s="170"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="B11:B18"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="I11:I18"/>
+    <mergeCell ref="I19:I23"/>
+    <mergeCell ref="I24:I27"/>
+    <mergeCell ref="I28:I31"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
@@ -5226,16 +5236,6 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="I3:I5"/>
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="I11:I18"/>
-    <mergeCell ref="I19:I23"/>
-    <mergeCell ref="I24:I27"/>
-    <mergeCell ref="I28:I31"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="B11:B18"/>
-    <mergeCell ref="B19:B23"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B24:B27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5260,47 +5260,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="144" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
       <c r="J1" s="71"/>
       <c r="K1" s="71"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="149" t="s">
+      <c r="A3" s="145" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="149" t="s">
+      <c r="B3" s="145" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="149" t="s">
+      <c r="C3" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="149" t="s">
+      <c r="D3" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="149"/>
-      <c r="F3" s="149"/>
-      <c r="G3" s="149"/>
-      <c r="H3" s="149" t="s">
+      <c r="E3" s="145"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="145"/>
+      <c r="H3" s="145" t="s">
         <v>263</v>
       </c>
-      <c r="I3" s="149" t="s">
+      <c r="I3" s="145" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="149"/>
-      <c r="B4" s="149"/>
-      <c r="C4" s="149"/>
+      <c r="A4" s="145"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="145"/>
       <c r="D4" s="75">
         <v>0</v>
       </c>
@@ -5313,13 +5313,13 @@
       <c r="G4" s="75">
         <v>3</v>
       </c>
-      <c r="H4" s="149"/>
-      <c r="I4" s="149"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
     </row>
     <row r="5" spans="1:11" ht="36" x14ac:dyDescent="0.35">
-      <c r="A5" s="149"/>
-      <c r="B5" s="150"/>
-      <c r="C5" s="150"/>
+      <c r="A5" s="145"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="146"/>
       <c r="D5" s="76" t="s">
         <v>4</v>
       </c>
@@ -5332,14 +5332,14 @@
       <c r="G5" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="149"/>
-      <c r="I5" s="149"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
     </row>
     <row r="6" spans="1:11" ht="90" x14ac:dyDescent="0.35">
-      <c r="A6" s="144">
+      <c r="A6" s="140">
         <v>1</v>
       </c>
-      <c r="B6" s="151" t="s">
+      <c r="B6" s="147" t="s">
         <v>238</v>
       </c>
       <c r="C6" s="70" t="s">
@@ -5357,8 +5357,8 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="54" x14ac:dyDescent="0.35">
-      <c r="A7" s="145"/>
-      <c r="B7" s="151"/>
+      <c r="A7" s="141"/>
+      <c r="B7" s="147"/>
       <c r="C7" s="56" t="s">
         <v>240</v>
       </c>
@@ -5374,8 +5374,8 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="72" x14ac:dyDescent="0.35">
-      <c r="A8" s="145"/>
-      <c r="B8" s="151"/>
+      <c r="A8" s="141"/>
+      <c r="B8" s="147"/>
       <c r="C8" s="56" t="s">
         <v>269</v>
       </c>
@@ -5391,8 +5391,8 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="36" x14ac:dyDescent="0.35">
-      <c r="A9" s="146"/>
-      <c r="B9" s="151"/>
+      <c r="A9" s="142"/>
+      <c r="B9" s="147"/>
       <c r="C9" s="56" t="s">
         <v>241</v>
       </c>
@@ -5408,10 +5408,10 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="72" x14ac:dyDescent="0.35">
-      <c r="A10" s="147">
+      <c r="A10" s="143">
         <v>2</v>
       </c>
-      <c r="B10" s="151" t="s">
+      <c r="B10" s="147" t="s">
         <v>243</v>
       </c>
       <c r="C10" s="70" t="s">
@@ -5429,8 +5429,8 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="72" x14ac:dyDescent="0.35">
-      <c r="A11" s="145"/>
-      <c r="B11" s="151"/>
+      <c r="A11" s="141"/>
+      <c r="B11" s="147"/>
       <c r="C11" s="56" t="s">
         <v>245</v>
       </c>
@@ -5446,8 +5446,8 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="36" x14ac:dyDescent="0.35">
-      <c r="A12" s="146"/>
-      <c r="B12" s="151"/>
+      <c r="A12" s="142"/>
+      <c r="B12" s="147"/>
       <c r="C12" s="70" t="s">
         <v>246</v>
       </c>
@@ -5463,10 +5463,10 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="54" x14ac:dyDescent="0.35">
-      <c r="A13" s="147">
+      <c r="A13" s="143">
         <v>3</v>
       </c>
-      <c r="B13" s="151" t="s">
+      <c r="B13" s="147" t="s">
         <v>248</v>
       </c>
       <c r="C13" s="59" t="s">
@@ -5482,8 +5482,8 @@
       <c r="I13" s="77"/>
     </row>
     <row r="14" spans="1:11" ht="54" x14ac:dyDescent="0.35">
-      <c r="A14" s="145"/>
-      <c r="B14" s="151"/>
+      <c r="A14" s="141"/>
+      <c r="B14" s="147"/>
       <c r="C14" s="59" t="s">
         <v>250</v>
       </c>
@@ -5497,8 +5497,8 @@
       <c r="I14" s="77"/>
     </row>
     <row r="15" spans="1:11" ht="54" x14ac:dyDescent="0.35">
-      <c r="A15" s="145"/>
-      <c r="B15" s="151"/>
+      <c r="A15" s="141"/>
+      <c r="B15" s="147"/>
       <c r="C15" s="70" t="s">
         <v>251</v>
       </c>
@@ -5514,8 +5514,8 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="72" x14ac:dyDescent="0.35">
-      <c r="A16" s="146"/>
-      <c r="B16" s="151"/>
+      <c r="A16" s="142"/>
+      <c r="B16" s="147"/>
       <c r="C16" s="59" t="s">
         <v>252</v>
       </c>
@@ -5529,10 +5529,10 @@
       <c r="I16" s="77"/>
     </row>
     <row r="17" spans="1:9" ht="54" x14ac:dyDescent="0.35">
-      <c r="A17" s="147">
+      <c r="A17" s="143">
         <v>4</v>
       </c>
-      <c r="B17" s="151" t="s">
+      <c r="B17" s="147" t="s">
         <v>254</v>
       </c>
       <c r="C17" s="59" t="s">
@@ -5548,8 +5548,8 @@
       <c r="I17" s="77"/>
     </row>
     <row r="18" spans="1:9" ht="36" x14ac:dyDescent="0.35">
-      <c r="A18" s="145"/>
-      <c r="B18" s="151"/>
+      <c r="A18" s="141"/>
+      <c r="B18" s="147"/>
       <c r="C18" s="59" t="s">
         <v>270</v>
       </c>
@@ -5563,8 +5563,8 @@
       <c r="I18" s="77"/>
     </row>
     <row r="19" spans="1:9" ht="72" x14ac:dyDescent="0.35">
-      <c r="A19" s="146"/>
-      <c r="B19" s="151"/>
+      <c r="A19" s="142"/>
+      <c r="B19" s="147"/>
       <c r="C19" s="59" t="s">
         <v>50</v>
       </c>
@@ -5620,45 +5620,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="130" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="163" t="s">
+      <c r="A3" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="163" t="s">
+      <c r="B3" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="163" t="s">
+      <c r="C3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="163" t="s">
+      <c r="D3" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163" t="s">
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
+      <c r="H3" s="131" t="s">
         <v>265</v>
       </c>
-      <c r="I3" s="163" t="s">
+      <c r="I3" s="131" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="163"/>
-      <c r="B4" s="163"/>
-      <c r="C4" s="163"/>
+      <c r="A4" s="131"/>
+      <c r="B4" s="131"/>
+      <c r="C4" s="131"/>
       <c r="D4" s="19">
         <v>0</v>
       </c>
@@ -5671,13 +5671,13 @@
       <c r="G4" s="19">
         <v>3</v>
       </c>
-      <c r="H4" s="163"/>
-      <c r="I4" s="163"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="131"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="163"/>
-      <c r="B5" s="164"/>
-      <c r="C5" s="164"/>
+      <c r="A5" s="131"/>
+      <c r="B5" s="132"/>
+      <c r="C5" s="132"/>
       <c r="D5" s="29" t="s">
         <v>4</v>
       </c>
@@ -5690,14 +5690,14 @@
       <c r="G5" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="163"/>
-      <c r="I5" s="163"/>
+      <c r="H5" s="131"/>
+      <c r="I5" s="131"/>
     </row>
     <row r="6" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="155">
+      <c r="A6" s="151">
         <v>1</v>
       </c>
-      <c r="B6" s="152" t="s">
+      <c r="B6" s="148" t="s">
         <v>271</v>
       </c>
       <c r="C6" s="85" t="s">
@@ -5715,8 +5715,8 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="156"/>
-      <c r="B7" s="153"/>
+      <c r="A7" s="152"/>
+      <c r="B7" s="149"/>
       <c r="C7" s="85" t="s">
         <v>274</v>
       </c>
@@ -5732,8 +5732,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="156"/>
-      <c r="B8" s="153"/>
+      <c r="A8" s="152"/>
+      <c r="B8" s="149"/>
       <c r="C8" s="85" t="s">
         <v>275</v>
       </c>
@@ -5749,8 +5749,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="156"/>
-      <c r="B9" s="153"/>
+      <c r="A9" s="152"/>
+      <c r="B9" s="149"/>
       <c r="C9" s="85" t="s">
         <v>291</v>
       </c>
@@ -5766,8 +5766,8 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="156"/>
-      <c r="B10" s="153"/>
+      <c r="A10" s="152"/>
+      <c r="B10" s="149"/>
       <c r="C10" s="85" t="s">
         <v>277</v>
       </c>
@@ -5783,8 +5783,8 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="156"/>
-      <c r="B11" s="153"/>
+      <c r="A11" s="152"/>
+      <c r="B11" s="149"/>
       <c r="C11" s="85" t="s">
         <v>278</v>
       </c>
@@ -5800,8 +5800,8 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="156"/>
-      <c r="B12" s="153"/>
+      <c r="A12" s="152"/>
+      <c r="B12" s="149"/>
       <c r="C12" s="86" t="s">
         <v>280</v>
       </c>
@@ -5817,8 +5817,8 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="157"/>
-      <c r="B13" s="154"/>
+      <c r="A13" s="133"/>
+      <c r="B13" s="150"/>
       <c r="C13" s="86" t="s">
         <v>282</v>
       </c>
@@ -5834,10 +5834,10 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="155">
+      <c r="A14" s="151">
         <v>2</v>
       </c>
-      <c r="B14" s="158" t="s">
+      <c r="B14" s="153" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="86" t="s">
@@ -5853,8 +5853,8 @@
       <c r="I14" s="24"/>
     </row>
     <row r="15" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="156"/>
-      <c r="B15" s="159"/>
+      <c r="A15" s="152"/>
+      <c r="B15" s="154"/>
       <c r="C15" s="86" t="s">
         <v>284</v>
       </c>
@@ -5868,8 +5868,8 @@
       <c r="I15" s="24"/>
     </row>
     <row r="16" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="156"/>
-      <c r="B16" s="159"/>
+      <c r="A16" s="152"/>
+      <c r="B16" s="154"/>
       <c r="C16" s="86" t="s">
         <v>52</v>
       </c>
@@ -5885,8 +5885,8 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="156"/>
-      <c r="B17" s="159"/>
+      <c r="A17" s="152"/>
+      <c r="B17" s="154"/>
       <c r="C17" s="86" t="s">
         <v>145</v>
       </c>
@@ -5902,8 +5902,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="156"/>
-      <c r="B18" s="159"/>
+      <c r="A18" s="152"/>
+      <c r="B18" s="154"/>
       <c r="C18" s="86" t="s">
         <v>285</v>
       </c>
@@ -5919,8 +5919,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="156"/>
-      <c r="B19" s="159"/>
+      <c r="A19" s="152"/>
+      <c r="B19" s="154"/>
       <c r="C19" s="86" t="s">
         <v>286</v>
       </c>
@@ -5936,8 +5936,8 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A20" s="157"/>
-      <c r="B20" s="160"/>
+      <c r="A20" s="133"/>
+      <c r="B20" s="155"/>
       <c r="C20" s="86" t="s">
         <v>287</v>
       </c>
@@ -5953,10 +5953,10 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A21" s="155">
+      <c r="A21" s="151">
         <v>3</v>
       </c>
-      <c r="B21" s="161" t="s">
+      <c r="B21" s="156" t="s">
         <v>288</v>
       </c>
       <c r="C21" s="86" t="s">
@@ -5974,8 +5974,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="156"/>
-      <c r="B22" s="162"/>
+      <c r="A22" s="152"/>
+      <c r="B22" s="157"/>
       <c r="C22" s="86" t="s">
         <v>290</v>
       </c>
@@ -5992,6 +5992,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B6:B13"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="B14:B20"/>
+    <mergeCell ref="A14:A20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A21:A22"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
@@ -5999,12 +6005,6 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="I3:I5"/>
-    <mergeCell ref="B6:B13"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="B14:B20"/>
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="A21:A22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6028,45 +6028,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="144" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
     </row>
     <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="170" t="s">
+      <c r="B2" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="171" t="s">
+      <c r="C2" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="170" t="s">
+      <c r="D2" s="158" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="173" t="s">
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="161" t="s">
         <v>259</v>
       </c>
-      <c r="I2" s="173" t="s">
+      <c r="I2" s="161" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="142"/>
-      <c r="B3" s="170"/>
-      <c r="C3" s="172"/>
+      <c r="A3" s="138"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="160"/>
       <c r="D3" s="90">
         <v>0</v>
       </c>
@@ -6079,13 +6079,13 @@
       <c r="G3" s="90">
         <v>3</v>
       </c>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
     </row>
     <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="142"/>
-      <c r="B4" s="143"/>
-      <c r="C4" s="146"/>
+      <c r="A4" s="138"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="142"/>
       <c r="D4" s="31" t="s">
         <v>4</v>
       </c>
@@ -6098,14 +6098,14 @@
       <c r="G4" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="161"/>
     </row>
     <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="168">
+      <c r="A5" s="165">
         <v>1</v>
       </c>
-      <c r="B5" s="165" t="s">
+      <c r="B5" s="162" t="s">
         <v>346</v>
       </c>
       <c r="C5" s="73" t="s">
@@ -6123,8 +6123,8 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="145"/>
-      <c r="B6" s="166"/>
+      <c r="A6" s="141"/>
+      <c r="B6" s="163"/>
       <c r="C6" s="73" t="s">
         <v>342</v>
       </c>
@@ -6140,8 +6140,8 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="145"/>
-      <c r="B7" s="166"/>
+      <c r="A7" s="141"/>
+      <c r="B7" s="163"/>
       <c r="C7" s="73" t="s">
         <v>345</v>
       </c>
@@ -6157,8 +6157,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" s="146"/>
-      <c r="B8" s="167"/>
+      <c r="A8" s="142"/>
+      <c r="B8" s="164"/>
       <c r="C8" s="73" t="s">
         <v>366</v>
       </c>
@@ -6174,10 +6174,10 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="168">
+      <c r="A9" s="165">
         <v>2</v>
       </c>
-      <c r="B9" s="161" t="s">
+      <c r="B9" s="156" t="s">
         <v>348</v>
       </c>
       <c r="C9" s="73" t="s">
@@ -6195,8 +6195,8 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="145"/>
-      <c r="B10" s="166"/>
+      <c r="A10" s="141"/>
+      <c r="B10" s="163"/>
       <c r="C10" s="73" t="s">
         <v>351</v>
       </c>
@@ -6212,8 +6212,8 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="145"/>
-      <c r="B11" s="166"/>
+      <c r="A11" s="141"/>
+      <c r="B11" s="163"/>
       <c r="C11" s="73" t="s">
         <v>353</v>
       </c>
@@ -6229,8 +6229,8 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="145"/>
-      <c r="B12" s="166"/>
+      <c r="A12" s="141"/>
+      <c r="B12" s="163"/>
       <c r="C12" s="73" t="s">
         <v>355</v>
       </c>
@@ -6246,8 +6246,8 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="145"/>
-      <c r="B13" s="166"/>
+      <c r="A13" s="141"/>
+      <c r="B13" s="163"/>
       <c r="C13" s="73" t="s">
         <v>357</v>
       </c>
@@ -6261,8 +6261,8 @@
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A14" s="145"/>
-      <c r="B14" s="166"/>
+      <c r="A14" s="141"/>
+      <c r="B14" s="163"/>
       <c r="C14" s="73" t="s">
         <v>358</v>
       </c>
@@ -6278,8 +6278,8 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="145"/>
-      <c r="B15" s="166"/>
+      <c r="A15" s="141"/>
+      <c r="B15" s="163"/>
       <c r="C15" s="73" t="s">
         <v>360</v>
       </c>
@@ -6295,8 +6295,8 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="145"/>
-      <c r="B16" s="166"/>
+      <c r="A16" s="141"/>
+      <c r="B16" s="163"/>
       <c r="C16" s="73" t="s">
         <v>361</v>
       </c>
@@ -6312,8 +6312,8 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="146"/>
-      <c r="B17" s="167"/>
+      <c r="A17" s="142"/>
+      <c r="B17" s="164"/>
       <c r="C17" s="73" t="s">
         <v>362</v>
       </c>
@@ -6329,10 +6329,10 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="168">
+      <c r="A18" s="165">
         <v>3</v>
       </c>
-      <c r="B18" s="165" t="s">
+      <c r="B18" s="162" t="s">
         <v>364</v>
       </c>
       <c r="C18" s="73" t="s">
@@ -6350,8 +6350,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="146"/>
-      <c r="B19" s="169"/>
+      <c r="A19" s="142"/>
+      <c r="B19" s="166"/>
       <c r="C19" s="73" t="s">
         <v>304</v>
       </c>
@@ -6368,6 +6368,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A9:A17"/>
+    <mergeCell ref="B9:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
@@ -6375,12 +6381,6 @@
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="A9:A17"/>
-    <mergeCell ref="B9:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6405,45 +6405,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="144" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="142" t="s">
+      <c r="A3" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="142" t="s">
+      <c r="B3" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="142" t="s">
+      <c r="C3" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="142" t="s">
+      <c r="D3" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="142"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="142"/>
-      <c r="H3" s="142" t="s">
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="142" t="s">
+      <c r="I3" s="138" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="142"/>
-      <c r="B4" s="142"/>
-      <c r="C4" s="142"/>
+      <c r="A4" s="138"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="138"/>
       <c r="D4" s="46">
         <v>0</v>
       </c>
@@ -6456,13 +6456,13 @@
       <c r="G4" s="46">
         <v>3</v>
       </c>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
     </row>
     <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="142"/>
-      <c r="B5" s="143"/>
-      <c r="C5" s="143"/>
+      <c r="A5" s="138"/>
+      <c r="B5" s="139"/>
+      <c r="C5" s="139"/>
       <c r="D5" s="32" t="s">
         <v>4</v>
       </c>
@@ -6475,14 +6475,14 @@
       <c r="G5" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="142"/>
-      <c r="I5" s="142"/>
+      <c r="H5" s="138"/>
+      <c r="I5" s="138"/>
     </row>
     <row r="6" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="168">
+      <c r="A6" s="165">
         <v>1</v>
       </c>
-      <c r="B6" s="174" t="s">
+      <c r="B6" s="167" t="s">
         <v>297</v>
       </c>
       <c r="C6" s="89" t="s">
@@ -6500,8 +6500,8 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="145"/>
-      <c r="B7" s="175"/>
+      <c r="A7" s="141"/>
+      <c r="B7" s="168"/>
       <c r="C7" s="89" t="s">
         <v>340</v>
       </c>
@@ -6517,8 +6517,8 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="145"/>
-      <c r="B8" s="175"/>
+      <c r="A8" s="141"/>
+      <c r="B8" s="168"/>
       <c r="C8" s="89" t="s">
         <v>299</v>
       </c>
@@ -6534,8 +6534,8 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="145"/>
-      <c r="B9" s="176"/>
+      <c r="A9" s="141"/>
+      <c r="B9" s="169"/>
       <c r="C9" s="91" t="s">
         <v>308</v>
       </c>
@@ -6551,8 +6551,8 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="145"/>
-      <c r="B10" s="176"/>
+      <c r="A10" s="141"/>
+      <c r="B10" s="169"/>
       <c r="C10" s="91" t="s">
         <v>306</v>
       </c>
@@ -6570,8 +6570,8 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" s="146"/>
-      <c r="B11" s="177"/>
+      <c r="A11" s="142"/>
+      <c r="B11" s="170"/>
       <c r="C11" s="91" t="s">
         <v>307</v>
       </c>
@@ -6587,10 +6587,10 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="144" x14ac:dyDescent="0.3">
-      <c r="A12" s="168">
+      <c r="A12" s="165">
         <v>2</v>
       </c>
-      <c r="B12" s="178" t="s">
+      <c r="B12" s="171" t="s">
         <v>309</v>
       </c>
       <c r="C12" s="91" t="s">
@@ -6611,8 +6611,8 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="145"/>
-      <c r="B13" s="179"/>
+      <c r="A13" s="141"/>
+      <c r="B13" s="172"/>
       <c r="C13" s="89" t="s">
         <v>312</v>
       </c>
@@ -6628,8 +6628,8 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A14" s="145"/>
-      <c r="B14" s="179"/>
+      <c r="A14" s="141"/>
+      <c r="B14" s="172"/>
       <c r="C14" s="89" t="s">
         <v>313</v>
       </c>
@@ -6645,8 +6645,8 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="145"/>
-      <c r="B15" s="179"/>
+      <c r="A15" s="141"/>
+      <c r="B15" s="172"/>
       <c r="C15" s="89" t="s">
         <v>314</v>
       </c>
@@ -6662,8 +6662,8 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="146"/>
-      <c r="B16" s="180"/>
+      <c r="A16" s="142"/>
+      <c r="B16" s="173"/>
       <c r="C16" s="92" t="s">
         <v>315</v>
       </c>
@@ -6679,10 +6679,10 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="144" x14ac:dyDescent="0.3">
-      <c r="A17" s="168">
+      <c r="A17" s="165">
         <v>3</v>
       </c>
-      <c r="B17" s="174" t="s">
+      <c r="B17" s="167" t="s">
         <v>316</v>
       </c>
       <c r="C17" s="89" t="s">
@@ -6700,8 +6700,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="145"/>
-      <c r="B18" s="175"/>
+      <c r="A18" s="141"/>
+      <c r="B18" s="168"/>
       <c r="C18" s="89" t="s">
         <v>319</v>
       </c>
@@ -6717,8 +6717,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="145"/>
-      <c r="B19" s="176"/>
+      <c r="A19" s="141"/>
+      <c r="B19" s="169"/>
       <c r="C19" s="89" t="s">
         <v>320</v>
       </c>
@@ -6734,8 +6734,8 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="146"/>
-      <c r="B20" s="180"/>
+      <c r="A20" s="142"/>
+      <c r="B20" s="173"/>
       <c r="C20" s="89" t="s">
         <v>321</v>
       </c>
@@ -6752,6 +6752,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B6:B11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A6:A11"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="A17:A20"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
@@ -6759,12 +6765,6 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="I3:I5"/>
-    <mergeCell ref="B6:B11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="A17:A20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6792,17 +6792,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
     </row>
     <row r="2" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="99"/>
@@ -6817,32 +6817,32 @@
       <c r="K2" s="71"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="188" t="s">
+      <c r="A3" s="181" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="188" t="s">
+      <c r="B3" s="181" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="188" t="s">
+      <c r="C3" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="188" t="s">
+      <c r="D3" s="181" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="188"/>
-      <c r="F3" s="188"/>
-      <c r="G3" s="188"/>
-      <c r="H3" s="188" t="s">
+      <c r="E3" s="181"/>
+      <c r="F3" s="181"/>
+      <c r="G3" s="181"/>
+      <c r="H3" s="181" t="s">
         <v>259</v>
       </c>
-      <c r="I3" s="188" t="s">
+      <c r="I3" s="181" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="188"/>
-      <c r="B4" s="188"/>
-      <c r="C4" s="188"/>
+      <c r="A4" s="181"/>
+      <c r="B4" s="181"/>
+      <c r="C4" s="181"/>
       <c r="D4" s="49">
         <v>0</v>
       </c>
@@ -6855,14 +6855,14 @@
       <c r="G4" s="49">
         <v>3</v>
       </c>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
+      <c r="H4" s="181"/>
+      <c r="I4" s="181"/>
       <c r="K4" s="101"/>
     </row>
     <row r="5" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="188"/>
-      <c r="B5" s="189"/>
-      <c r="C5" s="189"/>
+      <c r="A5" s="181"/>
+      <c r="B5" s="182"/>
+      <c r="C5" s="182"/>
       <c r="D5" s="49" t="s">
         <v>4</v>
       </c>
@@ -6875,14 +6875,14 @@
       <c r="G5" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="188"/>
-      <c r="I5" s="188"/>
+      <c r="H5" s="181"/>
+      <c r="I5" s="181"/>
     </row>
     <row r="6" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="182">
+      <c r="A6" s="175">
         <v>1</v>
       </c>
-      <c r="B6" s="165" t="s">
+      <c r="B6" s="162" t="s">
         <v>375</v>
       </c>
       <c r="C6" s="86" t="s">
@@ -6895,13 +6895,13 @@
       <c r="H6" s="106" t="s">
         <v>378</v>
       </c>
-      <c r="I6" s="185" t="s">
+      <c r="I6" s="178" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="184"/>
-      <c r="B7" s="169"/>
+      <c r="A7" s="177"/>
+      <c r="B7" s="166"/>
       <c r="C7" s="86" t="s">
         <v>377</v>
       </c>
@@ -6912,13 +6912,13 @@
       <c r="H7" s="106" t="s">
         <v>379</v>
       </c>
-      <c r="I7" s="186"/>
+      <c r="I7" s="179"/>
     </row>
     <row r="8" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="182">
+      <c r="A8" s="175">
         <v>2</v>
       </c>
-      <c r="B8" s="165" t="s">
+      <c r="B8" s="162" t="s">
         <v>380</v>
       </c>
       <c r="C8" s="113" t="s">
@@ -6931,11 +6931,11 @@
       <c r="H8" s="106" t="s">
         <v>399</v>
       </c>
-      <c r="I8" s="186"/>
+      <c r="I8" s="179"/>
     </row>
     <row r="9" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="183"/>
-      <c r="B9" s="190"/>
+      <c r="A9" s="176"/>
+      <c r="B9" s="183"/>
       <c r="C9" s="113" t="s">
         <v>386</v>
       </c>
@@ -6946,11 +6946,11 @@
       <c r="H9" s="106" t="s">
         <v>400</v>
       </c>
-      <c r="I9" s="186"/>
+      <c r="I9" s="179"/>
     </row>
     <row r="10" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="184"/>
-      <c r="B10" s="169"/>
+      <c r="A10" s="177"/>
+      <c r="B10" s="166"/>
       <c r="C10" s="113" t="s">
         <v>387</v>
       </c>
@@ -6961,11 +6961,11 @@
       <c r="H10" s="106" t="s">
         <v>401</v>
       </c>
-      <c r="I10" s="186"/>
+      <c r="I10" s="179"/>
     </row>
     <row r="11" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="114"/>
-      <c r="B11" s="181" t="s">
+      <c r="B11" s="174" t="s">
         <v>388</v>
       </c>
       <c r="C11" s="113" t="s">
@@ -6978,13 +6978,13 @@
       <c r="H11" s="106" t="s">
         <v>402</v>
       </c>
-      <c r="I11" s="186"/>
+      <c r="I11" s="179"/>
     </row>
     <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="182">
+      <c r="A12" s="175">
         <v>3</v>
       </c>
-      <c r="B12" s="166"/>
+      <c r="B12" s="163"/>
       <c r="C12" s="113" t="s">
         <v>389</v>
       </c>
@@ -6995,11 +6995,11 @@
       <c r="H12" s="73" t="s">
         <v>403</v>
       </c>
-      <c r="I12" s="186"/>
+      <c r="I12" s="179"/>
     </row>
     <row r="13" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="183"/>
-      <c r="B13" s="166"/>
+      <c r="A13" s="176"/>
+      <c r="B13" s="163"/>
       <c r="C13" s="113" t="s">
         <v>390</v>
       </c>
@@ -7010,11 +7010,11 @@
       <c r="H13" s="73" t="s">
         <v>404</v>
       </c>
-      <c r="I13" s="186"/>
+      <c r="I13" s="179"/>
     </row>
     <row r="14" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="183"/>
-      <c r="B14" s="166"/>
+      <c r="A14" s="176"/>
+      <c r="B14" s="163"/>
       <c r="C14" s="113" t="s">
         <v>405</v>
       </c>
@@ -7025,11 +7025,11 @@
       <c r="H14" s="106" t="s">
         <v>406</v>
       </c>
-      <c r="I14" s="186"/>
+      <c r="I14" s="179"/>
     </row>
     <row r="15" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="183"/>
-      <c r="B15" s="166"/>
+      <c r="A15" s="176"/>
+      <c r="B15" s="163"/>
       <c r="C15" s="113" t="s">
         <v>393</v>
       </c>
@@ -7040,11 +7040,11 @@
       <c r="H15" s="27" t="s">
         <v>407</v>
       </c>
-      <c r="I15" s="186"/>
+      <c r="I15" s="179"/>
     </row>
     <row r="16" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="183"/>
-      <c r="B16" s="166"/>
+      <c r="A16" s="176"/>
+      <c r="B16" s="163"/>
       <c r="C16" s="113" t="s">
         <v>391</v>
       </c>
@@ -7055,13 +7055,13 @@
       <c r="H16" s="106" t="s">
         <v>408</v>
       </c>
-      <c r="I16" s="186"/>
+      <c r="I16" s="179"/>
     </row>
     <row r="17" spans="1:9" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="182">
+      <c r="A17" s="175">
         <v>4</v>
       </c>
-      <c r="B17" s="165" t="s">
+      <c r="B17" s="162" t="s">
         <v>398</v>
       </c>
       <c r="C17" s="113" t="s">
@@ -7074,11 +7074,11 @@
       <c r="H17" s="106" t="s">
         <v>409</v>
       </c>
-      <c r="I17" s="186"/>
+      <c r="I17" s="179"/>
     </row>
     <row r="18" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="183"/>
-      <c r="B18" s="166"/>
+      <c r="A18" s="176"/>
+      <c r="B18" s="163"/>
       <c r="C18" s="73" t="s">
         <v>396</v>
       </c>
@@ -7089,11 +7089,11 @@
       <c r="H18" s="73" t="s">
         <v>410</v>
       </c>
-      <c r="I18" s="187"/>
+      <c r="I18" s="180"/>
     </row>
     <row r="19" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A19" s="184"/>
-      <c r="B19" s="167"/>
+      <c r="A19" s="177"/>
+      <c r="B19" s="164"/>
       <c r="C19" s="86" t="s">
         <v>397</v>
       </c>
@@ -7170,29 +7170,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="B1" s="132" t="s">
+      <c r="B1" s="130" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
       <c r="K1" s="16"/>
       <c r="L1" s="16"/>
     </row>
     <row r="3" spans="1:12" s="107" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="108"/>
       <c r="C3" s="108"/>
-      <c r="D3" s="193" t="s">
+      <c r="D3" s="186" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="193"/>
-      <c r="F3" s="193"/>
-      <c r="G3" s="193"/>
+      <c r="E3" s="186"/>
+      <c r="F3" s="186"/>
+      <c r="G3" s="186"/>
       <c r="H3" s="108"/>
     </row>
     <row r="4" spans="1:12" s="107" customFormat="1" x14ac:dyDescent="0.3">
@@ -7234,10 +7234,10 @@
       <c r="I5" s="109"/>
     </row>
     <row r="6" spans="1:12" s="107" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="191">
+      <c r="A6" s="184">
         <v>1</v>
       </c>
-      <c r="B6" s="197" t="s">
+      <c r="B6" s="190" t="s">
         <v>412</v>
       </c>
       <c r="C6" s="73" t="s">
@@ -7253,8 +7253,8 @@
       <c r="I6" s="111"/>
     </row>
     <row r="7" spans="1:12" s="107" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="191"/>
-      <c r="B7" s="198"/>
+      <c r="A7" s="184"/>
+      <c r="B7" s="191"/>
       <c r="C7" s="73" t="s">
         <v>383</v>
       </c>
@@ -7268,8 +7268,8 @@
       <c r="I7" s="111"/>
     </row>
     <row r="8" spans="1:12" s="107" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="191"/>
-      <c r="B8" s="198"/>
+      <c r="A8" s="184"/>
+      <c r="B8" s="191"/>
       <c r="C8" s="73" t="s">
         <v>384</v>
       </c>
@@ -7283,8 +7283,8 @@
       <c r="I8" s="111"/>
     </row>
     <row r="9" spans="1:12" s="107" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="191"/>
-      <c r="B9" s="198"/>
+      <c r="A9" s="184"/>
+      <c r="B9" s="191"/>
       <c r="C9" s="73" t="s">
         <v>415</v>
       </c>
@@ -7298,8 +7298,8 @@
       <c r="I9" s="111"/>
     </row>
     <row r="10" spans="1:12" s="107" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="191"/>
-      <c r="B10" s="199"/>
+      <c r="A10" s="184"/>
+      <c r="B10" s="192"/>
       <c r="C10" s="73" t="s">
         <v>416</v>
       </c>
@@ -7313,10 +7313,10 @@
       <c r="I10" s="111"/>
     </row>
     <row r="11" spans="1:12" s="107" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" s="192">
+      <c r="A11" s="185">
         <v>2</v>
       </c>
-      <c r="B11" s="194" t="s">
+      <c r="B11" s="187" t="s">
         <v>417</v>
       </c>
       <c r="C11" s="73" t="s">
@@ -7332,8 +7332,8 @@
       <c r="I11" s="111"/>
     </row>
     <row r="12" spans="1:12" s="107" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="192"/>
-      <c r="B12" s="194"/>
+      <c r="A12" s="185"/>
+      <c r="B12" s="187"/>
       <c r="C12" s="73" t="s">
         <v>419</v>
       </c>
@@ -7347,8 +7347,8 @@
       <c r="I12" s="111"/>
     </row>
     <row r="13" spans="1:12" s="107" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="192"/>
-      <c r="B13" s="194"/>
+      <c r="A13" s="185"/>
+      <c r="B13" s="187"/>
       <c r="C13" s="93" t="s">
         <v>420</v>
       </c>
@@ -7362,8 +7362,8 @@
       <c r="I13" s="111"/>
     </row>
     <row r="14" spans="1:12" s="107" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A14" s="192"/>
-      <c r="B14" s="194"/>
+      <c r="A14" s="185"/>
+      <c r="B14" s="187"/>
       <c r="C14" s="93" t="s">
         <v>421</v>
       </c>
@@ -7377,10 +7377,10 @@
       <c r="I14" s="111"/>
     </row>
     <row r="15" spans="1:12" s="107" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="192">
+      <c r="A15" s="185">
         <v>3</v>
       </c>
-      <c r="B15" s="138" t="s">
+      <c r="B15" s="134" t="s">
         <v>422</v>
       </c>
       <c r="C15" s="116" t="s">
@@ -7396,8 +7396,8 @@
       <c r="I15" s="111"/>
     </row>
     <row r="16" spans="1:12" s="107" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="192"/>
-      <c r="B16" s="195"/>
+      <c r="A16" s="185"/>
+      <c r="B16" s="188"/>
       <c r="C16" s="86" t="s">
         <v>423</v>
       </c>
@@ -7411,8 +7411,8 @@
       <c r="I16" s="111"/>
     </row>
     <row r="17" spans="1:9" s="107" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="192"/>
-      <c r="B17" s="140"/>
+      <c r="A17" s="185"/>
+      <c r="B17" s="136"/>
       <c r="C17" s="117" t="s">
         <v>424</v>
       </c>
@@ -7426,10 +7426,10 @@
       <c r="I17" s="111"/>
     </row>
     <row r="18" spans="1:9" s="107" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="192">
+      <c r="A18" s="185">
         <v>4</v>
       </c>
-      <c r="B18" s="196" t="s">
+      <c r="B18" s="189" t="s">
         <v>425</v>
       </c>
       <c r="C18" s="73" t="s">
@@ -7445,8 +7445,8 @@
       <c r="I18" s="111"/>
     </row>
     <row r="19" spans="1:9" s="107" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="192"/>
-      <c r="B19" s="196"/>
+      <c r="A19" s="185"/>
+      <c r="B19" s="189"/>
       <c r="C19" s="73" t="s">
         <v>426</v>
       </c>
@@ -7460,8 +7460,8 @@
       <c r="I19" s="111"/>
     </row>
     <row r="20" spans="1:9" s="107" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="192"/>
-      <c r="B20" s="196"/>
+      <c r="A20" s="185"/>
+      <c r="B20" s="189"/>
       <c r="C20" s="73" t="s">
         <v>427</v>
       </c>
@@ -7526,45 +7526,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="201" t="s">
+      <c r="A1" s="198" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="201"/>
-      <c r="C1" s="201"/>
-      <c r="D1" s="201"/>
-      <c r="E1" s="201"/>
-      <c r="F1" s="201"/>
-      <c r="G1" s="201"/>
-      <c r="H1" s="201"/>
-      <c r="I1" s="201"/>
+      <c r="B1" s="198"/>
+      <c r="C1" s="198"/>
+      <c r="D1" s="198"/>
+      <c r="E1" s="198"/>
+      <c r="F1" s="198"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="200" t="s">
+      <c r="A3" s="195" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="200" t="s">
+      <c r="B3" s="195" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="200" t="s">
+      <c r="C3" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="200" t="s">
+      <c r="D3" s="195" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="200"/>
-      <c r="H3" s="200" t="s">
+      <c r="E3" s="195"/>
+      <c r="F3" s="195"/>
+      <c r="G3" s="195"/>
+      <c r="H3" s="195" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="200" t="s">
+      <c r="I3" s="195" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="200"/>
-      <c r="B4" s="200"/>
-      <c r="C4" s="200"/>
+      <c r="A4" s="195"/>
+      <c r="B4" s="195"/>
+      <c r="C4" s="195"/>
       <c r="D4" s="121">
         <v>0</v>
       </c>
@@ -7577,13 +7577,13 @@
       <c r="G4" s="121">
         <v>3</v>
       </c>
-      <c r="H4" s="200"/>
-      <c r="I4" s="200"/>
+      <c r="H4" s="195"/>
+      <c r="I4" s="195"/>
     </row>
     <row r="5" spans="1:9" ht="36" x14ac:dyDescent="0.3">
-      <c r="A5" s="200"/>
-      <c r="B5" s="202"/>
-      <c r="C5" s="202"/>
+      <c r="A5" s="195"/>
+      <c r="B5" s="193"/>
+      <c r="C5" s="193"/>
       <c r="D5" s="122" t="s">
         <v>4</v>
       </c>
@@ -7596,12 +7596,12 @@
       <c r="G5" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="200"/>
-      <c r="I5" s="200"/>
+      <c r="H5" s="195"/>
+      <c r="I5" s="195"/>
     </row>
     <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.3">
-      <c r="A6" s="200"/>
-      <c r="B6" s="204" t="s">
+      <c r="A6" s="195"/>
+      <c r="B6" s="196" t="s">
         <v>448</v>
       </c>
       <c r="C6" s="123" t="s">
@@ -7619,8 +7619,8 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" s="205"/>
-      <c r="B7" s="205"/>
+      <c r="A7" s="197"/>
+      <c r="B7" s="197"/>
       <c r="C7" s="123" t="s">
         <v>450</v>
       </c>
@@ -7634,8 +7634,8 @@
       <c r="I7" s="126"/>
     </row>
     <row r="8" spans="1:9" ht="54" x14ac:dyDescent="0.3">
-      <c r="A8" s="205"/>
-      <c r="B8" s="205"/>
+      <c r="A8" s="197"/>
+      <c r="B8" s="197"/>
       <c r="C8" s="123" t="s">
         <v>451</v>
       </c>
@@ -7649,8 +7649,8 @@
       <c r="I8" s="126"/>
     </row>
     <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.3">
-      <c r="A9" s="205"/>
-      <c r="B9" s="205"/>
+      <c r="A9" s="197"/>
+      <c r="B9" s="197"/>
       <c r="C9" s="123" t="s">
         <v>452</v>
       </c>
@@ -7664,8 +7664,8 @@
       <c r="I9" s="126"/>
     </row>
     <row r="10" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A10" s="202"/>
-      <c r="B10" s="203" t="s">
+      <c r="A10" s="193"/>
+      <c r="B10" s="194" t="s">
         <v>443</v>
       </c>
       <c r="C10" s="123" t="s">
@@ -7683,8 +7683,8 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" s="202"/>
-      <c r="B11" s="203"/>
+      <c r="A11" s="193"/>
+      <c r="B11" s="194"/>
       <c r="C11" s="123" t="s">
         <v>77</v>
       </c>
@@ -7698,8 +7698,8 @@
       <c r="I11" s="124"/>
     </row>
     <row r="12" spans="1:9" ht="54" x14ac:dyDescent="0.3">
-      <c r="A12" s="202"/>
-      <c r="B12" s="203"/>
+      <c r="A12" s="193"/>
+      <c r="B12" s="194"/>
       <c r="C12" s="123" t="s">
         <v>78</v>
       </c>
@@ -7715,8 +7715,8 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="54" x14ac:dyDescent="0.3">
-      <c r="A13" s="200"/>
-      <c r="B13" s="203" t="s">
+      <c r="A13" s="195"/>
+      <c r="B13" s="194" t="s">
         <v>460</v>
       </c>
       <c r="C13" s="123" t="s">
@@ -7734,8 +7734,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="162" x14ac:dyDescent="0.3">
-      <c r="A14" s="202"/>
-      <c r="B14" s="203"/>
+      <c r="A14" s="193"/>
+      <c r="B14" s="194"/>
       <c r="C14" s="123" t="s">
         <v>83</v>
       </c>
@@ -7751,8 +7751,8 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A15" s="202"/>
-      <c r="B15" s="203"/>
+      <c r="A15" s="193"/>
+      <c r="B15" s="194"/>
       <c r="C15" s="123" t="s">
         <v>81</v>
       </c>
@@ -7768,8 +7768,8 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="108" x14ac:dyDescent="0.3">
-      <c r="A16" s="202"/>
-      <c r="B16" s="203"/>
+      <c r="A16" s="193"/>
+      <c r="B16" s="194"/>
       <c r="C16" s="123" t="s">
         <v>82</v>
       </c>
@@ -7785,8 +7785,8 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="54" x14ac:dyDescent="0.3">
-      <c r="A17" s="202"/>
-      <c r="B17" s="203" t="s">
+      <c r="A17" s="193"/>
+      <c r="B17" s="194" t="s">
         <v>444</v>
       </c>
       <c r="C17" s="123" t="s">
@@ -7804,8 +7804,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="54" x14ac:dyDescent="0.3">
-      <c r="A18" s="202"/>
-      <c r="B18" s="203"/>
+      <c r="A18" s="193"/>
+      <c r="B18" s="194"/>
       <c r="C18" s="123" t="s">
         <v>446</v>
       </c>
@@ -7821,8 +7821,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="90" x14ac:dyDescent="0.3">
-      <c r="A19" s="202"/>
-      <c r="B19" s="203"/>
+      <c r="A19" s="193"/>
+      <c r="B19" s="194"/>
       <c r="C19" s="123" t="s">
         <v>447</v>
       </c>
@@ -7839,6 +7839,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="H3:H5"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="A13:A16"/>
@@ -7847,13 +7854,6 @@
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="B13:B16"/>
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="H3:H5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -7881,47 +7881,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="130" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="133" t="s">
+      <c r="A3" s="204" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="133" t="s">
+      <c r="B3" s="204" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="133" t="s">
+      <c r="C3" s="204" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="133" t="s">
+      <c r="D3" s="204" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="133" t="s">
+      <c r="E3" s="204"/>
+      <c r="F3" s="204"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="133" t="s">
+      <c r="I3" s="204" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="133"/>
-      <c r="B4" s="133"/>
-      <c r="C4" s="133"/>
+      <c r="A4" s="204"/>
+      <c r="B4" s="204"/>
+      <c r="C4" s="204"/>
       <c r="D4" s="34">
         <v>0</v>
       </c>
@@ -7934,13 +7934,13 @@
       <c r="G4" s="34">
         <v>3</v>
       </c>
-      <c r="H4" s="133"/>
-      <c r="I4" s="133"/>
+      <c r="H4" s="204"/>
+      <c r="I4" s="204"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="133"/>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134"/>
+      <c r="A5" s="204"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="205"/>
       <c r="D5" s="34" t="s">
         <v>4</v>
       </c>
@@ -7953,14 +7953,14 @@
       <c r="G5" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
+      <c r="H5" s="204"/>
+      <c r="I5" s="204"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="34">
         <v>1</v>
       </c>
-      <c r="B6" s="127" t="s">
+      <c r="B6" s="199" t="s">
         <v>84</v>
       </c>
       <c r="C6" s="35" t="s">
@@ -7973,13 +7973,13 @@
       <c r="H6" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="I6" s="135" t="s">
+      <c r="I6" s="206" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="34"/>
-      <c r="B7" s="128"/>
+      <c r="B7" s="200"/>
       <c r="C7" s="35" t="s">
         <v>86</v>
       </c>
@@ -7990,13 +7990,13 @@
       <c r="H7" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="I7" s="136"/>
+      <c r="I7" s="207"/>
     </row>
     <row r="8" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34">
         <v>2</v>
       </c>
-      <c r="B8" s="128"/>
+      <c r="B8" s="200"/>
       <c r="C8" s="35" t="s">
         <v>87</v>
       </c>
@@ -8007,13 +8007,13 @@
       <c r="H8" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="I8" s="136"/>
+      <c r="I8" s="207"/>
     </row>
     <row r="9" spans="1:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>3</v>
       </c>
-      <c r="B9" s="129" t="s">
+      <c r="B9" s="201" t="s">
         <v>88</v>
       </c>
       <c r="C9" s="35" t="s">
@@ -8026,11 +8026,11 @@
       <c r="H9" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="I9" s="136"/>
+      <c r="I9" s="207"/>
     </row>
     <row r="10" spans="1:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34"/>
-      <c r="B10" s="130"/>
+      <c r="B10" s="202"/>
       <c r="C10" s="35" t="s">
         <v>110</v>
       </c>
@@ -8041,11 +8041,11 @@
       <c r="H10" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="I10" s="136"/>
+      <c r="I10" s="207"/>
     </row>
     <row r="11" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="43"/>
-      <c r="B11" s="130"/>
+      <c r="B11" s="202"/>
       <c r="C11" s="35" t="s">
         <v>90</v>
       </c>
@@ -8056,11 +8056,11 @@
       <c r="H11" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="I11" s="136"/>
+      <c r="I11" s="207"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="34"/>
-      <c r="B12" s="130"/>
+      <c r="B12" s="202"/>
       <c r="C12" s="35" t="s">
         <v>91</v>
       </c>
@@ -8071,11 +8071,11 @@
       <c r="H12" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="I12" s="136"/>
+      <c r="I12" s="207"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="34"/>
-      <c r="B13" s="131"/>
+      <c r="B13" s="203"/>
       <c r="C13" s="35" t="s">
         <v>92</v>
       </c>
@@ -8086,7 +8086,7 @@
       <c r="H13" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="I13" s="136"/>
+      <c r="I13" s="207"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="34"/>
@@ -8101,13 +8101,13 @@
       <c r="H14" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="I14" s="136"/>
+      <c r="I14" s="207"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>4</v>
       </c>
-      <c r="B15" s="129" t="s">
+      <c r="B15" s="201" t="s">
         <v>94</v>
       </c>
       <c r="C15" s="35" t="s">
@@ -8120,11 +8120,11 @@
       <c r="H15" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="I15" s="136"/>
+      <c r="I15" s="207"/>
     </row>
     <row r="16" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="43"/>
-      <c r="B16" s="130"/>
+      <c r="B16" s="202"/>
       <c r="C16" s="35" t="s">
         <v>95</v>
       </c>
@@ -8135,11 +8135,11 @@
       <c r="H16" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="I16" s="136"/>
+      <c r="I16" s="207"/>
     </row>
     <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="43"/>
-      <c r="B17" s="131"/>
+      <c r="B17" s="203"/>
       <c r="C17" s="35" t="s">
         <v>116</v>
       </c>
@@ -8150,7 +8150,7 @@
       <c r="H17" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="I17" s="137"/>
+      <c r="I17" s="208"/>
     </row>
     <row r="21" spans="1:9" ht="35.4" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
